--- a/ru/downloads/data-excel/16.1.4.xlsx
+++ b/ru/downloads/data-excel/16.1.4.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Глобальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Глобальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14175" windowHeight="8070"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -988,14 +988,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="36.85546875" style="8" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>19</v>
       </c>
@@ -1008,7 +1008,7 @@
       <c r="D1" s="26"/>
       <c r="E1" s="26"/>
     </row>
-    <row r="2" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1021,14 +1021,14 @@
       <c r="D2" s="26"/>
       <c r="E2" s="26"/>
     </row>
-    <row r="3" spans="1:9" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="26"/>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
       <c r="D3" s="26"/>
       <c r="E3" s="26"/>
     </row>
-    <row r="4" spans="1:9" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -1056,8 +1056,11 @@
       <c r="I4" s="46">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J4" s="46">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="39" t="s">
         <v>69</v>
       </c>
@@ -1085,8 +1088,11 @@
       <c r="I5" s="47">
         <v>69.935153262375351</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J5" s="47">
+        <v>76.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="40" t="s">
         <v>20</v>
       </c>
@@ -1102,8 +1108,9 @@
       <c r="G6" s="21"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
-    </row>
-    <row r="7" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J6" s="7"/>
+    </row>
+    <row r="7" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="42" t="s">
         <v>22</v>
       </c>
@@ -1131,8 +1138,11 @@
       <c r="I7" s="7">
         <v>66.022628049505357</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J7" s="7">
+        <v>68.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="42" t="s">
         <v>24</v>
       </c>
@@ -1160,8 +1170,11 @@
       <c r="I8" s="7">
         <v>72.445373516489639</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J8" s="7">
+        <v>82.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="40" t="s">
         <v>75</v>
       </c>
@@ -1177,8 +1190,9 @@
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
       <c r="I9" s="7"/>
-    </row>
-    <row r="10" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J9" s="7"/>
+    </row>
+    <row r="10" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="14" t="s">
         <v>26</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="I10" s="7">
         <v>77.693880449605857</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J10" s="7">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
         <v>27</v>
       </c>
@@ -1235,8 +1252,11 @@
       <c r="I11" s="7">
         <v>58.471470669068943</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J11" s="7">
+        <v>64.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="37" t="s">
         <v>66</v>
       </c>
@@ -1252,8 +1272,9 @@
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
       <c r="I12" s="7"/>
-    </row>
-    <row r="13" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J12" s="7"/>
+    </row>
+    <row r="13" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
         <v>28</v>
       </c>
@@ -1281,8 +1302,11 @@
       <c r="I13" s="7">
         <v>73.922135395602709</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J13" s="7">
+        <v>64.099999999999994</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
@@ -1310,8 +1334,11 @@
       <c r="I14" s="7">
         <v>66.937405400906428</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J14" s="7">
+        <v>67.400000000000006</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="14" t="s">
         <v>34</v>
       </c>
@@ -1339,8 +1366,11 @@
       <c r="I15" s="7">
         <v>73.557500333162565</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J15" s="7">
+        <v>78.400000000000006</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="14" t="s">
         <v>37</v>
       </c>
@@ -1368,8 +1398,11 @@
       <c r="I16" s="7">
         <v>81.455700661236804</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J16" s="7">
+        <v>94.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="15" t="s">
         <v>40</v>
       </c>
@@ -1397,8 +1430,11 @@
       <c r="I17" s="7">
         <v>85.326100153863408</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J17" s="7">
+        <v>93.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="15" t="s">
         <v>43</v>
       </c>
@@ -1426,8 +1462,11 @@
       <c r="I18" s="7">
         <v>93.58161545143426</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J18" s="7">
+        <v>93.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="43" t="s">
         <v>46</v>
       </c>
@@ -1455,8 +1494,11 @@
       <c r="I19" s="7">
         <v>45.863239000214556</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J19" s="7">
+        <v>71.400000000000006</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="11" t="s">
         <v>49</v>
       </c>
@@ -1484,8 +1526,11 @@
       <c r="I20" s="7">
         <v>57.948304848793633</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J20" s="7">
+        <v>60.9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="11" t="s">
         <v>52</v>
       </c>
@@ -1513,8 +1558,11 @@
       <c r="I21" s="7">
         <v>99.882024854774457</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J21" s="7">
+        <v>99.1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="35" t="s">
         <v>82</v>
       </c>
@@ -1530,8 +1578,9 @@
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
-    </row>
-    <row r="23" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J22" s="7"/>
+    </row>
+    <row r="23" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="11" t="s">
         <v>55</v>
       </c>
@@ -1559,8 +1608,11 @@
       <c r="I23" s="7">
         <v>70.691370116293825</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J23" s="7">
+        <v>77.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="11" t="s">
         <v>84</v>
       </c>
@@ -1588,8 +1640,11 @@
       <c r="I24" s="7">
         <v>71.098645225987312</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J24" s="7">
+        <v>76.400000000000006</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="11" t="s">
         <v>87</v>
       </c>
@@ -1617,8 +1672,11 @@
       <c r="I25" s="7">
         <v>64.89475521079099</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J25" s="7">
+        <v>74.099999999999994</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="35" t="s">
         <v>90</v>
       </c>
@@ -1634,8 +1692,9 @@
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
       <c r="I26" s="7"/>
-    </row>
-    <row r="27" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J26" s="7"/>
+    </row>
+    <row r="27" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="11" t="s">
         <v>92</v>
       </c>
@@ -1663,8 +1722,11 @@
       <c r="I27" s="7">
         <v>65.622675838865561</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J27" s="7">
+        <v>80.900000000000006</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="11" t="s">
         <v>58</v>
       </c>
@@ -1692,8 +1754,11 @@
       <c r="I28" s="7">
         <v>73.433152357092524</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J28" s="7">
+        <v>80.2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="43" t="s">
         <v>59</v>
       </c>
@@ -1721,8 +1786,11 @@
       <c r="I29" s="7">
         <v>70.983653046322218</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J29" s="7">
+        <v>76.3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="42" t="s">
         <v>96</v>
       </c>
@@ -1750,8 +1818,11 @@
       <c r="I30" s="7">
         <v>67.351453404966563</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J30" s="7">
+        <v>75.7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="44" t="s">
         <v>98</v>
       </c>
@@ -1779,8 +1850,11 @@
       <c r="I31" s="7">
         <v>68.419794065398122</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J31" s="7">
+        <v>73.7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="40" t="s">
         <v>100</v>
       </c>
@@ -1796,8 +1870,9 @@
       <c r="G32" s="24"/>
       <c r="H32" s="24"/>
       <c r="I32" s="24"/>
-    </row>
-    <row r="33" spans="1:9" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J32" s="24"/>
+    </row>
+    <row r="33" spans="1:10" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="42" t="s">
         <v>102</v>
       </c>
@@ -1825,8 +1900,11 @@
       <c r="I33" s="7">
         <v>70.130693762003517</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J33" s="7">
+        <v>80.900000000000006</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="42" t="s">
         <v>104</v>
       </c>
@@ -1854,8 +1932,11 @@
       <c r="I34" s="7">
         <v>72.588098755387108</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J34" s="7">
+        <v>80.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="42" t="s">
         <v>106</v>
       </c>
@@ -1883,8 +1964,11 @@
       <c r="I35" s="7">
         <v>66.388091151087039</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J35" s="7">
+        <v>76.3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="42" t="s">
         <v>108</v>
       </c>
@@ -1912,8 +1996,11 @@
       <c r="I36" s="7">
         <v>69.181634969678541</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J36" s="7">
+        <v>75.7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="45" t="s">
         <v>61</v>
       </c>
@@ -1941,8 +2028,11 @@
       <c r="I37" s="51">
         <v>71.420434847949394</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" s="55" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J37" s="51">
+        <v>73.7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" s="55" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="52" t="s">
         <v>62</v>
       </c>
@@ -1955,57 +2045,57 @@
       <c r="D38" s="54"/>
       <c r="E38" s="54"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" s="18"/>
       <c r="B39" s="6"/>
       <c r="C39" s="10"/>
       <c r="D39" s="7"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" s="18"/>
       <c r="B40" s="6"/>
       <c r="C40" s="10"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="18"/>
       <c r="B42" s="6"/>
       <c r="C42" s="10"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="18"/>
       <c r="B43" s="6"/>
       <c r="C43" s="10"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="12"/>
       <c r="B44" s="5"/>
       <c r="C44" s="12"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="16"/>
       <c r="B45" s="6"/>
       <c r="C45" s="10"/>
       <c r="D45" s="7"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="16"/>
       <c r="B46" s="6"/>
       <c r="C46" s="10"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="16"/>
       <c r="B47" s="6"/>
       <c r="C47" s="10"/>
       <c r="D47" s="7"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="20"/>
       <c r="B48" s="6"/>
       <c r="C48" s="10"/>
